--- a/Assignment data/mtDNA_files/assignment_mtDNA_MappingReport.xlsx
+++ b/Assignment data/mtDNA_files/assignment_mtDNA_MappingReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelzor/GoogleDrive/Durham/2021-2024_PDRA/2022-2023-Teaching/IBA/Assignment/mtDNA_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelzor/GoogleDrive/Github/Introductory-ancient-DNA-practical/Assignment data/mtDNA_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5970E30F-47AF-D144-AC99-235DE9260A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E46A9E-66E5-5549-90FB-F57370744D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34100" yWindow="980" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mtDNAMappingReport" sheetId="1" r:id="rId1"/>
@@ -33,35 +33,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Sample Name</t>
   </si>
   <si>
-    <t>Total reads or read pairs</t>
-  </si>
-  <si>
-    <t>Total retained reads or read pairs after trimming (and merging for ancient)</t>
-  </si>
-  <si>
-    <t>Proportion kept after trimming (and merging)</t>
-  </si>
-  <si>
-    <t>Mapped reads</t>
-  </si>
-  <si>
-    <t>Mean Cov</t>
-  </si>
-  <si>
-    <t>SD Cov</t>
-  </si>
-  <si>
     <t>%ref covered at &gt;=1x</t>
   </si>
   <si>
-    <t>%ref covered at &gt;=5x</t>
-  </si>
-  <si>
     <t>UF100</t>
   </si>
   <si>
@@ -74,12 +53,6 @@
     <t>UF104</t>
   </si>
   <si>
-    <t>0.1141X</t>
-  </si>
-  <si>
-    <t>0.3618X</t>
-  </si>
-  <si>
     <t>UF11</t>
   </si>
   <si>
@@ -104,12 +77,6 @@
     <t>UF703</t>
   </si>
   <si>
-    <t>1.1951X</t>
-  </si>
-  <si>
-    <t>2.0615X</t>
-  </si>
-  <si>
     <t>UF8</t>
   </si>
   <si>
@@ -119,53 +86,65 @@
     <t>UF801</t>
   </si>
   <si>
-    <t>3.6209X</t>
-  </si>
-  <si>
-    <t>2.0308X</t>
-  </si>
-  <si>
     <t>UF802</t>
   </si>
   <si>
     <t>UF803</t>
   </si>
   <si>
-    <t>Q25 mapped</t>
-  </si>
-  <si>
-    <t>Q25 mapped reads after duplicate removal</t>
-  </si>
-  <si>
-    <t>Avg length of mapped Q25 reads</t>
-  </si>
-  <si>
-    <t>Cluster factor (Mapped Q25 reads/ Unique Q25 mapped reads)</t>
-  </si>
-  <si>
-    <t>5' first base C-&gt;T frequency</t>
-  </si>
-  <si>
-    <t>5' second base C-&gt;T frequency</t>
-  </si>
-  <si>
-    <t>3' first base G-&gt;A frequency</t>
-  </si>
-  <si>
-    <t>3' second base G-&gt;A frequency</t>
-  </si>
-  <si>
-    <t>Endogenous content (Mapped reads/Total reads or read pairs)</t>
+    <t>Nr. Input reads</t>
+  </si>
+  <si>
+    <t>Nr. Reads into Mapping (post trimming and merging)</t>
+  </si>
+  <si>
+    <t>Proportion kept after trimming and merging (reads into mapping/input reads)</t>
+  </si>
+  <si>
+    <t>Nr. Mapped Reads Passed Post-Filter</t>
+  </si>
+  <si>
+    <t>Post-DeDup Mapped Reads</t>
+  </si>
+  <si>
+    <t>ClusterFactor (value representing how many duplicates in the library exist for each unique read)</t>
+  </si>
+  <si>
+    <t>Mean length of mapped reads</t>
+  </si>
+  <si>
+    <t>Mean coverage</t>
+  </si>
+  <si>
+    <t>%ref covered at &gt;=3x</t>
+  </si>
+  <si>
+    <t>3 Prime G&gt;A 1st base (%)</t>
+  </si>
+  <si>
+    <t>5 Prime C&gt;T 1st base (%)</t>
+  </si>
+  <si>
+    <t>Endogenous DNA (%) (mapped reads/reads into mapping)</t>
+  </si>
+  <si>
+    <t>UF102</t>
+  </si>
+  <si>
+    <t>0.1X</t>
+  </si>
+  <si>
+    <t>1.4X</t>
+  </si>
+  <si>
+    <t>3.8X</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -300,6 +279,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.8"/>
+      <color rgb="FF333333"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -482,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -597,21 +596,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -657,7 +641,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -665,24 +649,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -742,9 +724,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -782,7 +764,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -888,7 +870,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1030,7 +1012,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1038,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="13" width="10.83203125" style="2"/>
@@ -1046,628 +1028,588 @@
     <col min="15" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="153" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="144" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B2" s="6">
+        <v>2772296</v>
+      </c>
+      <c r="C2" s="7">
+        <v>2324777</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B3" s="7">
+        <v>28731857</v>
+      </c>
+      <c r="C3" s="7">
+        <v>22830259</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="7">
+        <v>3823834</v>
+      </c>
+      <c r="C4" s="7">
+        <v>3318405</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="B5" s="7">
+        <v>6540074</v>
+      </c>
+      <c r="C5" s="7">
+        <v>5775041</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>3020661</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2285371</v>
+      </c>
+      <c r="D6" s="5">
+        <f t="shared" ref="D3:D19" si="0">ROUND(C6/B6,2)</f>
+        <v>0.76</v>
+      </c>
+      <c r="E6" s="8">
+        <v>44</v>
+      </c>
+      <c r="F6" s="8">
+        <v>28</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1.36</v>
+      </c>
+      <c r="H6" s="5">
+        <v>71</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J6" s="9">
+        <v>0.107</v>
+      </c>
+      <c r="K6" s="9">
+        <v>1E-3</v>
+      </c>
+      <c r="L6" s="9">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7">
+        <v>23951543</v>
+      </c>
+      <c r="C7" s="7">
+        <v>20548311</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7">
+        <v>2674012</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2305341</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7">
+        <v>28790082</v>
+      </c>
+      <c r="C9" s="7">
+        <v>22819419</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>30946190</v>
+      </c>
+      <c r="C10" s="7">
+        <v>28726574</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7">
+        <v>10297151</v>
+      </c>
+      <c r="C11" s="7">
+        <v>8627262</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7">
+        <v>10373990</v>
+      </c>
+      <c r="C12" s="7">
+        <v>9247261</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7">
+        <v>4863388</v>
+      </c>
+      <c r="C13" s="7">
+        <v>4121009</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7">
+        <v>32009877</v>
+      </c>
+      <c r="C14" s="7">
+        <v>27625645</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.86</v>
+      </c>
+      <c r="E14" s="8">
+        <v>406</v>
+      </c>
+      <c r="F14" s="8">
+        <v>365</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H14" s="5">
+        <v>62</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J14" s="9">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7">
+        <v>28688669</v>
+      </c>
+      <c r="C15" s="7">
+        <v>24407752</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="5"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7">
+        <v>79768678</v>
+      </c>
+      <c r="C16" s="7">
+        <v>67293000</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7">
+        <v>39325539</v>
+      </c>
+      <c r="C17" s="7">
+        <v>28814405</v>
+      </c>
+      <c r="D17" s="5">
+        <f t="shared" si="0"/>
+        <v>0.73</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1159</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1006</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="H17" s="5">
+        <v>62</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4">
-        <v>2772296</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4">
-        <v>114</v>
-      </c>
-      <c r="F2" s="4">
-        <v>113</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="4">
-        <v>28731857</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>8787</v>
-      </c>
-      <c r="F3" s="4">
-        <v>8787</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="4">
-        <v>6540074</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4">
-        <v>67</v>
-      </c>
-      <c r="F4" s="4">
-        <v>67</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3020661</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2097111</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.69</v>
-      </c>
-      <c r="E5" s="4">
-        <v>41</v>
-      </c>
-      <c r="F5" s="4">
-        <v>41</v>
-      </c>
-      <c r="G5" s="4">
-        <v>27</v>
-      </c>
-      <c r="H5" s="4">
-        <v>70</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0.10050000000000001</v>
-      </c>
-      <c r="L5" s="6">
+      <c r="J17" s="9">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="K17" s="9">
+        <v>0.70299999999999996</v>
+      </c>
+      <c r="L17" s="9">
+        <v>0.442</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="N17" s="8">
         <v>0</v>
       </c>
-      <c r="M5" s="4">
-        <v>1.51</v>
-      </c>
-      <c r="N5" s="8">
-        <f>E5/B5</f>
-        <v>1.357318812008365E-5</v>
-      </c>
-      <c r="O5" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="P5" s="7">
-        <v>0.28571428571428598</v>
-      </c>
-      <c r="Q5" s="7">
-        <v>8.3333333333333301E-2</v>
-      </c>
-      <c r="R5" s="7">
-        <v>9.0909090909090898E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="4">
-        <v>23951543</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
-        <v>658</v>
-      </c>
-      <c r="F6" s="4">
-        <v>658</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="4">
-        <v>2674012</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4">
-        <v>33</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="O17" s="5"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="4">
-        <v>6783919</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4">
-        <v>573</v>
-      </c>
-      <c r="F8" s="4">
-        <v>573</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="B18" s="7">
+        <v>1484158</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1333378</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="5"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="4">
-        <v>30946190</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4">
-        <v>1039</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1039</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="4">
-        <v>10297151</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4">
-        <v>87</v>
-      </c>
-      <c r="F10" s="4">
-        <v>87</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="4">
-        <v>10373990</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4">
-        <v>356</v>
-      </c>
-      <c r="F11" s="4">
-        <v>356</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="4">
-        <v>4863388</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4">
-        <v>375</v>
-      </c>
-      <c r="F12" s="4">
-        <v>375</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4">
-        <v>32009877</v>
-      </c>
-      <c r="C13" s="4">
-        <v>26370765</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.82</v>
-      </c>
-      <c r="E13" s="4">
-        <v>368</v>
-      </c>
-      <c r="F13" s="4">
-        <v>368</v>
-      </c>
-      <c r="G13" s="4">
-        <v>322</v>
-      </c>
-      <c r="H13" s="4">
-        <v>61.4938</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0.60670000000000002</v>
-      </c>
-      <c r="L13" s="5">
-        <v>2.06E-2</v>
-      </c>
-      <c r="M13" s="4">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="N13" s="8">
-        <f>E13/B13</f>
-        <v>1.1496451548376772E-5</v>
-      </c>
-      <c r="O13" s="7">
-        <v>0.31034482758620702</v>
-      </c>
-      <c r="P13" s="7">
-        <v>0.28169014084506999</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>0.317460317460317</v>
-      </c>
-      <c r="R13" s="7">
-        <v>9.6153846153846201E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="4">
-        <v>28688669</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4">
-        <v>97</v>
-      </c>
-      <c r="F14" s="4">
-        <v>97</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="4">
-        <v>79768678</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4">
-        <v>35</v>
-      </c>
-      <c r="F15" s="4">
-        <v>35</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="4">
-        <v>39325539</v>
-      </c>
-      <c r="C16" s="4">
-        <v>28211316</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0.71</v>
-      </c>
-      <c r="E16" s="4">
-        <v>1123</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1123</v>
-      </c>
-      <c r="G16" s="4">
-        <v>962</v>
-      </c>
-      <c r="H16" s="4">
-        <v>62.363799999999998</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="5">
-        <v>0.97360000000000002</v>
-      </c>
-      <c r="L16" s="5">
-        <v>0.28889999999999999</v>
-      </c>
-      <c r="M16" s="4">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="N16" s="8">
-        <f>E16/B16</f>
-        <v>2.8556506243944933E-5</v>
-      </c>
-      <c r="O16" s="7">
-        <v>0.40944881889763801</v>
-      </c>
-      <c r="P16" s="7">
-        <v>0.27155172413793099</v>
-      </c>
-      <c r="Q16" s="7">
-        <v>0.45248868778280499</v>
-      </c>
-      <c r="R16" s="7">
-        <v>0.24698795180722899</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="4">
-        <v>1484158</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4">
-        <v>3</v>
-      </c>
-      <c r="F17" s="4">
-        <v>3</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="4">
+      <c r="B19" s="7">
         <v>88646862</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4">
-        <v>1402</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1402</v>
-      </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
+      <c r="C19" s="7">
+        <v>82111946</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="5"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R18">
-    <sortCondition ref="A2:A18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N19">
+    <sortCondition ref="A2:A19"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
